--- a/stories/arbres/TREE-JEU-002.xlsx
+++ b/stories/arbres/TREE-JEU-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nino est dans le salon, avec maman. Deux chaussons font un but. Maman montre le tapis. C'est l'espace montré. Nino passe le ballon. Maman passe. Puis Nino pousse vers le but. But. Passer. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nino pose une pomme hors du tapis. Le fruit reste. Le jeu, c'est sur l'espace montré. Nino passe. Puis but. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On vise quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a visé le but. Nino a passé. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers la cuisine. La terre est un peu humide. Dans la cuisine, on refait un petit but de torchons. Espace montré. Passer. But. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2579,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2746,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. La lumière est claire. On souffle doucement. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2913,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3080,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. Des miettes dorment sur la table. On écoute jusqu'au bout. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3247,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3414,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. Un chat miaule une fois. On attend son tour. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3581,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3748,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le jardin. Le vent est doux sur la joue. Dans le jardin, deux cailloux. Espace montré. Nino passe. Vers le but. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3939,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3871,7 +3968,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nino garde les cubes tout près. Les chaussures font toc toc. On sourit ensemble. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range. Maman dit : c'est bien.</t>
+          <t>Nino garde les cubes tout près. Les chaussures font toc toc. On sourit ensemble. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4009,6 +4106,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. Les chaussures font toc toc. On sourit ensemble. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. La couverture est douce. On pose les pieds par terre. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. On souffle. Nino sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. Une cloche tinte au loin. On parle tout bas. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers la chambre. Le savon mousse entre les doigts. Dans la chambre, le tapis. Espace montré. Passer. But. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. Le bois sent le chaud. On range les jouets. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. Une goutte tombe, ploc. On s'assoit un moment. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. Le savon sent la fleur. On respire, un, deux. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6469,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nino pose un yaourt sur la table. Sur le tapis, l'espace montré. Nino passe le ballon. Vers le but. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6654,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Avant le but, on fait quoi avec le ballon ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6827,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Passer. But. Le tapis était l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7018,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6997,6 +7185,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers la cuisine. Un pain croustille. Ça sent le pain. Nino passe. But. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7376,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7207,7 +7405,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nino garde les cubes tout près. Le tissu est tout doux. On referme le sac. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range. Maman dit : c'est bien.</t>
+          <t>Nino garde les cubes tout près. Le tissu est tout doux. On referme le sac. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7345,6 +7543,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. Le tissu est tout doux. On referme le sac. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7711,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7878,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. Une cuillère tinte. On essuie une miette. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. On souffle. Nino sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8045,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8212,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. Le sable est tiède. On met le doudou près. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8379,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8546,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le jardin. Un rire court, tout petit. L'herbe est douce. Nino reste dans l'espace montré. Passer. But. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8737,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8904,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. Un rire court, tout petit. On lace les chaussures. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9071,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9238,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. Le papier froisse, chut. On met le manteau. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9405,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9572,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. L'herbe chatouille le mollet. On boit une gorgée. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9739,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9906,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers la chambre. Un rire court, tout petit. Le doudou est l'arbitre. Passer. But. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10097,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9847,7 +10126,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nino garde les cubes tout près. Un pigeon roucoule. On feuillette le livre. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range. Maman dit : c'est bien.</t>
+          <t>Nino garde les cubes tout près. Un pigeon roucoule. On feuillette le livre. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9985,6 +10264,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. Un pigeon roucoule. On feuillette le livre. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10432,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10599,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. La fenêtre vibre un peu. On referme le livre. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. On souffle. Nino sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10766,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10933,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. Le lait est froid dans le verre. On pose le ballon. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11100,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11267,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nino pose un morceau de pain. Maman rappelle : passer, but, espace montré. Nino reste sur le tapis. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11448,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On reste où ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11621,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit bravo. But. Passer. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11487,6 +11812,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11649,6 +11979,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers la cuisine. Ça sent le pain tiède. Nino pousse tout doux. But. Passer. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12170,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12337,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. La corde du sac est rêche. On secoue le sable. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12504,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12671,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. Le savon mousse entre les doigts. On caresse le tissu. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12838,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13005,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. Un ruisseau chante. On tend la main. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13172,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13339,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le jardin. Le vent est doux sur la joue. Une feuille tombe. On reste dans l'espace montré. Passer. But. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13530,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13179,7 +13559,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Nino garde les cubes tout près. La laine gratte un peu. On chante un petit air. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range. Maman dit : c'est bien.</t>
+          <t>Nino garde les cubes tout près. La laine gratte un peu. On chante un petit air. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13317,6 +13697,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. La laine gratte un peu. On chante un petit air. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13865,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14032,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. Un pain croustille. On compte jusqu'à trois. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. On souffle. Nino sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14199,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14366,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. Le savon glisse. On montre du doigt. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14533,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14151,7 +14562,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers la chambre. Ça sent le pain tiède. Nino range. Maman dit : but, passer, espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+          <t>Nino va vers la chambre. Ça sent le pain tiède. Nino range. But, passer, espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14289,6 +14700,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers la chambre. Ça sent le pain tiède. Nino range.
+maman|But, passer, espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14892,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15059,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde les cubes tout près. Une plume vole. On range la chaise. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15226,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15393,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde le livre tout près. Le banc est lisse. On range un objet. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15560,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15727,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nino garde la dînette tout près. Un grelot sonne. On se tient la main. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15894,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15482,6 +15934,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-002.xlsx
+++ b/stories/arbres/TREE-JEU-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Nino est dans le salon, avec maman. Deux chaussons font un but. Maman montre le tapis. C'est l'espace montré. Nino passe le ballon. Maman passe. Puis Nino pousse vers le but. But. Passer. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Nino pose une pomme hors du tapis. Le fruit reste. Le jeu, c'est sur l'espace montré. Nino passe. Puis but. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|On vise quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Nino a visé le but. Nino a passé. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Nino va vers la cuisine. La terre est un peu humide. Dans la cuisine, on refait un petit but de torchons. Espace montré. Passer. But. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2584,6 +2596,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2751,6 +2764,7 @@
           <t>narrateur|Nino garde les cubes tout près. La lumière est claire. On souffle doucement. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2918,6 +2932,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3085,6 +3100,7 @@
           <t>narrateur|Nino garde le livre tout près. Des miettes dorment sur la table. On écoute jusqu'au bout. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3252,6 +3268,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3419,6 +3436,7 @@
           <t>narrateur|Nino garde la dînette tout près. Un chat miaule une fois. On attend son tour. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3586,6 +3604,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3753,6 +3772,7 @@
           <t>narrateur|Nino va vers le jardin. Le vent est doux sur la joue. Dans le jardin, deux cailloux. Espace montré. Nino passe. Vers le but. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3944,6 +3964,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Nino garde le livre tout près. La couverture est douce. On pose les pieds par terre. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. On souffle. Nino sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Nino garde la dînette tout près. Une cloche tinte au loin. On parle tout bas. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Nino va vers la chambre. Le savon mousse entre les doigts. Dans la chambre, le tapis. Espace montré. Passer. But. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Nino garde les cubes tout près. Le bois sent le chaud. On range les jouets. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Nino garde le livre tout près. Une goutte tombe, ploc. On s'assoit un moment. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Nino garde la dînette tout près. Le savon sent la fleur. On respire, un, deux. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6474,6 +6509,7 @@
           <t>narrateur|Nino pose un yaourt sur la table. Sur le tapis, l'espace montré. Nino passe le ballon. Vers le but. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6661,6 +6697,7 @@
           <t>narrateur|Avant le but, on fait quoi avec le ballon ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6832,6 +6869,7 @@
           <t>narrateur|Passer. But. Le tapis était l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7023,6 +7061,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7190,6 +7229,7 @@
           <t>narrateur|Nino va vers la cuisine. Un pain croustille. Ça sent le pain. Nino passe. But. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7381,6 +7421,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7549,6 +7590,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7716,6 +7758,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7883,6 +7926,7 @@
           <t>narrateur|Nino garde le livre tout près. Une cuillère tinte. On essuie une miette. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. On souffle. Nino sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8050,6 +8094,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8217,6 +8262,7 @@
           <t>narrateur|Nino garde la dînette tout près. Le sable est tiède. On met le doudou près. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8384,6 +8430,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8551,6 +8598,7 @@
           <t>narrateur|Nino va vers le jardin. Un rire court, tout petit. L'herbe est douce. Nino reste dans l'espace montré. Passer. But. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8742,6 +8790,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8909,6 +8958,7 @@
           <t>narrateur|Nino garde les cubes tout près. Un rire court, tout petit. On lace les chaussures. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9076,6 +9126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9243,6 +9294,7 @@
           <t>narrateur|Nino garde le livre tout près. Le papier froisse, chut. On met le manteau. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9410,6 +9462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9577,6 +9630,7 @@
           <t>narrateur|Nino garde la dînette tout près. L'herbe chatouille le mollet. On boit une gorgée. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9744,6 +9798,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9911,6 +9966,7 @@
           <t>narrateur|Nino va vers la chambre. Un rire court, tout petit. Le doudou est l'arbitre. Passer. But. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10102,6 +10158,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10270,6 +10327,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10437,6 +10495,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10604,6 +10663,7 @@
           <t>narrateur|Nino garde le livre tout près. La fenêtre vibre un peu. On referme le livre. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. On souffle. Nino sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10771,6 +10831,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10938,6 +10999,7 @@
           <t>narrateur|Nino garde la dînette tout près. Le lait est froid dans le verre. On pose le ballon. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11105,6 +11167,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11272,6 +11335,7 @@
           <t>narrateur|Nino pose un morceau de pain. Maman rappelle : passer, but, espace montré. Nino reste sur le tapis. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11455,6 +11519,7 @@
           <t>narrateur|On reste où ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11626,6 +11691,7 @@
           <t>narrateur|Maman dit bravo. But. Passer. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11817,6 +11883,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11984,6 +12051,7 @@
           <t>narrateur|Nino va vers la cuisine. Ça sent le pain tiède. Nino pousse tout doux. But. Passer. Espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12175,6 +12243,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12342,6 +12411,7 @@
           <t>narrateur|Nino garde les cubes tout près. La corde du sac est rêche. On secoue le sable. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12509,6 +12579,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12676,6 +12747,7 @@
           <t>narrateur|Nino garde le livre tout près. Le savon mousse entre les doigts. On caresse le tissu. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12843,6 +12915,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13010,6 +13083,7 @@
           <t>narrateur|Nino garde la dînette tout près. Un ruisseau chante. On tend la main. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13177,6 +13251,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13344,6 +13419,7 @@
           <t>narrateur|Nino va vers le jardin. Le vent est doux sur la joue. Une feuille tombe. On reste dans l'espace montré. Passer. But. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13535,6 +13611,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13703,6 +13780,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13870,6 +13948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14037,6 +14116,7 @@
           <t>narrateur|Nino garde le livre tout près. Un pain croustille. On compte jusqu'à trois. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. On souffle. Nino sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14204,6 +14284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14371,6 +14452,7 @@
           <t>narrateur|Nino garde la dînette tout près. Le savon glisse. On montre du doigt. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les pieds étaient dans l'espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14538,6 +14620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14706,6 +14789,7 @@
 maman|But, passer, espace montré. On vise le but. On se passe le ballon. On reste dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14897,6 +14981,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15064,6 +15149,7 @@
           <t>narrateur|Nino garde les cubes tout près. Une plume vole. On range la chaise. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Les chaussons sont le but. On vise le but. On se passe le ballon. On reste dans l'espace montré. Nino dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15231,6 +15317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15398,6 +15485,7 @@
           <t>narrateur|Nino garde le livre tout près. Le banc est lisse. On range un objet. On a visé le but. On s'est passé le ballon. Dans l'espace montré. Le tapis est rangé. On vise le but. On se passe le ballon. On reste dans l'espace montré. Maman serre Nino tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15565,6 +15653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15732,6 +15821,7 @@
           <t>narrateur|Nino garde la dînette tout près. Un grelot sonne. On se tient la main. On a visé le but. On s'est passé le ballon. Dans l'espace montré. On a dit bravo. On vise le but. On se passe le ballon. On reste dans l'espace montré. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15899,6 +15989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15917,7 +16008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15941,6 +16032,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15955,7 +16060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16142,6 +16247,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
